--- a/input/260421-reemplazo.xlsx
+++ b/input/260421-reemplazo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soledadaraya/Library/CloudStorage/Dropbox/Lucía Miranda Fondecyt/femocratas/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AEBAA9-6F3A-6C49-B733-265757320D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6131367B-C23F-D945-90DB-7D9AB54314A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{55250885-A9CC-0540-A48D-8746377425B8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="302">
   <si>
     <t>concepto</t>
   </si>
@@ -780,6 +780,168 @@
   </si>
   <si>
     <t>áreas</t>
+  </si>
+  <si>
+    <t>candidatura</t>
+  </si>
+  <si>
+    <t>candidaturas</t>
+  </si>
+  <si>
+    <t>católica</t>
+  </si>
+  <si>
+    <t>católicas</t>
+  </si>
+  <si>
+    <t>católico</t>
+  </si>
+  <si>
+    <t>categoría</t>
+  </si>
+  <si>
+    <t>categorías</t>
+  </si>
+  <si>
+    <t>catedrática</t>
+  </si>
+  <si>
+    <t>catedrático</t>
+  </si>
+  <si>
+    <t>académico</t>
+  </si>
+  <si>
+    <t>académica</t>
+  </si>
+  <si>
+    <t>académicas</t>
+  </si>
+  <si>
+    <t>académicos</t>
+  </si>
+  <si>
+    <t>academia</t>
+  </si>
+  <si>
+    <t>académico/a</t>
+  </si>
+  <si>
+    <t>cuidadora</t>
+  </si>
+  <si>
+    <t>cuidadoras</t>
+  </si>
+  <si>
+    <t>cuota</t>
+  </si>
+  <si>
+    <t>cuotas</t>
+  </si>
+  <si>
+    <t>curriculum</t>
+  </si>
+  <si>
+    <t>currículum</t>
+  </si>
+  <si>
+    <t>debate</t>
+  </si>
+  <si>
+    <t>debates</t>
+  </si>
+  <si>
+    <t>decidido</t>
+  </si>
+  <si>
+    <t>decreto</t>
+  </si>
+  <si>
+    <t>decretos</t>
+  </si>
+  <si>
+    <t>dedicado</t>
+  </si>
+  <si>
+    <t>dedicar</t>
+  </si>
+  <si>
+    <t>dedicarme</t>
+  </si>
+  <si>
+    <t>dediqué</t>
+  </si>
+  <si>
+    <t>defender</t>
+  </si>
+  <si>
+    <t>defendiendo</t>
+  </si>
+  <si>
+    <t>defiendo</t>
+  </si>
+  <si>
+    <t>definición</t>
+  </si>
+  <si>
+    <t>definir</t>
+  </si>
+  <si>
+    <t>delito</t>
+  </si>
+  <si>
+    <t>delitos</t>
+  </si>
+  <si>
+    <t>demanda</t>
+  </si>
+  <si>
+    <t>demandas</t>
+  </si>
+  <si>
+    <t>democracias</t>
+  </si>
+  <si>
+    <t>departamento</t>
+  </si>
+  <si>
+    <t>departamentos</t>
+  </si>
+  <si>
+    <t>derechos_sexuales</t>
+  </si>
+  <si>
+    <t>derechos_sexuales_y_reproductivos</t>
+  </si>
+  <si>
+    <t>derecho_al_aborto</t>
+  </si>
+  <si>
+    <t>desigualdad</t>
+  </si>
+  <si>
+    <t>desigualdades</t>
+  </si>
+  <si>
+    <t>diferencia</t>
+  </si>
+  <si>
+    <t>diferencias</t>
+  </si>
+  <si>
+    <t>dinámica</t>
+  </si>
+  <si>
+    <t>dinámicas</t>
+  </si>
+  <si>
+    <t>diplomáticas</t>
+  </si>
+  <si>
+    <t>diplomáticos</t>
+  </si>
+  <si>
+    <t>diplomático/as</t>
   </si>
 </sst>
 </file>
@@ -821,7 +983,408 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="40">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1151,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D04AA13-B37D-EB42-A4A3-F11DCBAD5BFD}">
-  <dimension ref="A1:B247"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.5" customWidth="1"/>
@@ -1735,23 +2298,23 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
         <v>77</v>
@@ -1759,7 +2322,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
         <v>77</v>
@@ -1767,31 +2330,31 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B80" t="s">
         <v>80</v>
@@ -1799,7 +2362,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B81" t="s">
         <v>80</v>
@@ -1807,7 +2370,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B82" t="s">
         <v>80</v>
@@ -1815,39 +2378,39 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B87" t="s">
         <v>87</v>
@@ -1855,23 +2418,23 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B90" t="s">
         <v>91</v>
@@ -1879,87 +2442,87 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B101" t="s">
         <v>103</v>
@@ -1967,103 +2530,103 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B106" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B114" t="s">
         <v>115</v>
@@ -2071,7 +2634,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B115" t="s">
         <v>115</v>
@@ -2079,55 +2642,55 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B120" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B122" t="s">
         <v>122</v>
@@ -2135,39 +2698,39 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B127" t="s">
         <v>128</v>
@@ -2175,23 +2738,23 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B130" t="s">
         <v>130</v>
@@ -2199,55 +2762,55 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B135" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B137" t="s">
         <v>138</v>
@@ -2255,7 +2818,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B138" t="s">
         <v>138</v>
@@ -2263,23 +2826,23 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B141" t="s">
         <v>147</v>
@@ -2287,7 +2850,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B142" t="s">
         <v>147</v>
@@ -2295,7 +2858,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B143" t="s">
         <v>147</v>
@@ -2303,7 +2866,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B144" t="s">
         <v>147</v>
@@ -2311,7 +2874,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B145" t="s">
         <v>147</v>
@@ -2319,39 +2882,39 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B146" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B148" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B150" t="s">
         <v>152</v>
@@ -2359,87 +2922,87 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B151" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B153" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B155" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B157" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B159" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B161" t="s">
         <v>163</v>
@@ -2447,7 +3010,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B162" t="s">
         <v>163</v>
@@ -2455,7 +3018,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B163" t="s">
         <v>163</v>
@@ -2463,7 +3026,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B164" t="s">
         <v>163</v>
@@ -2471,87 +3034,87 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B166" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B167" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B169" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B171" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B173" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B175" t="s">
         <v>176</v>
@@ -2559,7 +3122,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B176" t="s">
         <v>176</v>
@@ -2567,39 +3130,39 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B178" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B181" t="s">
         <v>186</v>
@@ -2607,7 +3170,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B182" t="s">
         <v>186</v>
@@ -2615,7 +3178,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B183" t="s">
         <v>186</v>
@@ -2623,7 +3186,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B184" t="s">
         <v>186</v>
@@ -2631,7 +3194,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B185" t="s">
         <v>186</v>
@@ -2639,7 +3202,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B186" t="s">
         <v>186</v>
@@ -2647,87 +3210,87 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B188" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B191" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B195" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B197" t="s">
         <v>199</v>
@@ -2735,7 +3298,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B198" t="s">
         <v>199</v>
@@ -2743,39 +3306,39 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B203" t="s">
         <v>203</v>
@@ -2783,7 +3346,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B204" t="s">
         <v>203</v>
@@ -2791,79 +3354,79 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B205" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B206" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B207" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B209" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B213" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B214" t="s">
         <v>216</v>
@@ -2871,79 +3434,79 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B215" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B218" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B220" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B222" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B224" t="s">
         <v>225</v>
@@ -2951,7 +3514,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B225" t="s">
         <v>225</v>
@@ -2959,23 +3522,23 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B227" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B228" t="s">
         <v>228</v>
@@ -2983,7 +3546,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B229" t="s">
         <v>228</v>
@@ -2991,23 +3554,23 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B230" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B231" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B232" t="s">
         <v>233</v>
@@ -3015,7 +3578,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B233" t="s">
         <v>233</v>
@@ -3023,71 +3586,71 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B235" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B238" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B240" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B242" t="s">
         <v>243</v>
@@ -3095,7 +3658,7 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B243" t="s">
         <v>243</v>
@@ -3103,37 +3666,565 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B245" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B246" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>250</v>
+      </c>
+      <c r="B248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>251</v>
+      </c>
+      <c r="B249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>252</v>
+      </c>
+      <c r="B250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>253</v>
+      </c>
+      <c r="B251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>254</v>
+      </c>
+      <c r="B252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>255</v>
+      </c>
+      <c r="B253" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>256</v>
+      </c>
+      <c r="B254" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>257</v>
+      </c>
+      <c r="B255" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>258</v>
+      </c>
+      <c r="B256" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>259</v>
+      </c>
+      <c r="B257" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>260</v>
+      </c>
+      <c r="B258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>261</v>
+      </c>
+      <c r="B259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>207</v>
+      </c>
+      <c r="B298" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A265:A278 A260:A263 A1:A258 A299:A1048576 A280:A297">
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B247">
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B246">
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B248">
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B249">
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B250">
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B252">
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B251">
+    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B261">
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B260">
+    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B263">
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B262">
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B267:B268">
+    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B266">
+    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B270">
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B269">
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B271">
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B272">
+    <cfRule type="duplicateValues" dxfId="22" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B273">
+    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B274">
+    <cfRule type="duplicateValues" dxfId="20" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B275">
+    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B276">
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B277">
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B278">
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B281">
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B280">
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B283">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B282">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B286">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B285">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B287">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B288">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B289">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B291">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B290">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B293">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B292">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B295">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B294">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>